--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>14.285714285714</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.461538461538</v>
+        <v>-43.75</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.636363636363</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.919191919191</v>
+        <v>-91.588785046729</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
+        <v>15</v>
+      </c>
+      <c r="J17" s="14">
         <v>13</v>
       </c>
-      <c r="J17" s="14">
-        <v>10</v>
-      </c>
       <c r="K17" s="15">
-        <v>30</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L17" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>85.714285714285</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.478260869565</v>
+        <v>-34.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>109.090909090909</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>75</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>7.692307692307</v>
+        <v>10</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" s="15">
-        <v>-63.157894736842</v>
+        <v>-63.333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
         <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.5</v>
+        <v>-31.25</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.114754098360</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.791666666666</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.858407079646</v>
+        <v>-31.782945736434</v>
       </c>
       <c r="M19" s="15">
         <v>-26.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.442622950819</v>
+        <v>-69.759450171821</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15">
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15">
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.842105263157</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.391304347826</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="F21" s="17">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>13.414634146341</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.526717557251</v>
+        <v>-6.875</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.818181818181</v>
+        <v>-23.195876288659</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.214285714285</v>
+        <v>-20.744680851063</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.022304832713</v>
+        <v>-76.006441223832</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>-53.846153846153</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>11.881188118811</v>
+        <v>-0.970873786407</v>
       </c>
       <c r="I24" s="14">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="J24" s="14">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.108108108108</v>
+        <v>-14.835164835164</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.047619047619</v>
+        <v>-20.918367346938</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.375796178343</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>28.571428571428</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F25" s="14">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.792207792207</v>
+        <v>-20.481927710843</v>
       </c>
       <c r="I25" s="14">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J25" s="14">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.074074074074</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.145985401459</v>
+        <v>-40</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-72.727272727272</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>-37.5</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="I26" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J26" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K26" s="15">
-        <v>6.25</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.108108108108</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="M26" s="15">
-        <v>100</v>
+        <v>94.736842105263</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-62.5</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L28" s="15">
         <v>-25</v>
-      </c>
-      <c r="L28" s="15">
-        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1499,8 +1499,8 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1540,8 +1540,8 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.75</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.869565217391</v>
+        <v>-48</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.588785046729</v>
+        <v>-89.516129032258</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>15.384615384615</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="M17" s="15">
-        <v>66.666666666666</v>
+        <v>70</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.782608695652</v>
+        <v>-34.615384615384</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>57.142857142857</v>
+        <v>65.217391304347</v>
       </c>
       <c r="L18" s="15">
-        <v>10</v>
+        <v>18.75</v>
       </c>
       <c r="M18" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-63.333333333333</v>
+        <v>-62.745098039215</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
         <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-31.25</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.254237288135</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.428571428571</v>
+        <v>-19.53125</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.782945736434</v>
+        <v>-29.931972789115</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.666666666666</v>
+        <v>-24.817518248175</v>
       </c>
       <c r="N19" s="15">
-        <v>-69.759450171821</v>
+        <v>-68.209876543209</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1125,13 +1125,13 @@
         <v>100</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
         <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.581196581196</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.931034482758</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.818181818181</v>
+        <v>-3.370786516853</v>
       </c>
       <c r="I21" s="17">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.875</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.195876288659</v>
+        <v>-19.724770642201</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.744680851063</v>
+        <v>-18.981481481481</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.006441223832</v>
+        <v>-74.820143884892</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>6</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>-37.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-27.272727272727</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L22" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-43.75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.176470588235</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.970873786407</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I24" s="14">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="J24" s="14">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.835164835164</v>
+        <v>-14.150943396226</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.918367346938</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="M24" s="15">
-        <v>-16.666666666666</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-46.153846153846</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F25" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G25" s="14">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.481927710843</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="I25" s="14">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.358208955223</v>
+        <v>-26.143790849673</v>
       </c>
       <c r="L25" s="15">
-        <v>-40</v>
+        <v>-41.752577319587</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>-57.142857142857</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>-48.148148148148</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I26" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J26" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.128205128205</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.756097560975</v>
+        <v>-18</v>
       </c>
       <c r="M26" s="15">
-        <v>94.736842105263</v>
+        <v>51.851851851851</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,26 +1557,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -904,11 +904,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.777777777777</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M16" s="15">
-        <v>-48</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.516129032258</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="15">
-        <v>83.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" s="15">
-        <v>21.428571428571</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>70</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.615384615384</v>
+        <v>-32.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>65.217391304347</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>18.75</v>
+        <v>2.439024390243</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>2.439024390243</v>
       </c>
       <c r="N18" s="15">
-        <v>-62.745098039215</v>
+        <v>-64.705882352941</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.836065573770</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="I19" s="14">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.53125</v>
+        <v>-17.931034482758</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.931972789115</v>
+        <v>-27.439024390243</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.817518248175</v>
+        <v>-20.134228187919</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.209876543209</v>
+        <v>-67.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.581196581196</v>
+        <v>-96.212121212121</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.370786516853</v>
+        <v>-12.371134020618</v>
       </c>
       <c r="I21" s="17">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="J21" s="17">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.777777777777</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.724770642201</v>
+        <v>-20.948616600790</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.981481481481</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.820143884892</v>
+        <v>-74.358974358974</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.181818181818</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M22" s="15">
-        <v>-43.75</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.333333333333</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F24" s="14">
+        <v>96</v>
+      </c>
+      <c r="G24" s="14">
         <v>108</v>
       </c>
-      <c r="G24" s="14">
-        <v>114</v>
-      </c>
       <c r="H24" s="15">
-        <v>-5.263157894736</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="J24" s="14">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.150943396226</v>
+        <v>-15.677966101694</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.212121212121</v>
+        <v>-24.334600760456</v>
       </c>
       <c r="M24" s="15">
-        <v>-16.129032258064</v>
+        <v>-14.957264957265</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-10.526315789473</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F25" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.476190476190</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="I25" s="14">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="J25" s="14">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.143790849673</v>
+        <v>-26.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.752577319587</v>
+        <v>-41.284403669724</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>-31.818181818181</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J26" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="L26" s="15">
-        <v>-18</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="M26" s="15">
-        <v>51.851851851851</v>
+        <v>51.612903225806</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1411,8 +1411,8 @@
       <c r="K27" s="15">
         <v>100</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+      <c r="L27" s="15">
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,22 +1438,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-45.454545454545</v>
+        <v>-62.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-45.454545454545</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1570,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -910,23 +910,23 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,22 +934,22 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-30</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
@@ -961,54 +961,54 @@
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.782608695652</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.275862068965</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.384615384615</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>2</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>20</v>
+      </c>
+      <c r="J17" s="14">
+        <v>16</v>
+      </c>
+      <c r="K17" s="15">
+        <v>25</v>
+      </c>
+      <c r="L17" s="15">
+        <v>5.263157894736</v>
+      </c>
+      <c r="M17" s="15">
         <v>42.857142857142</v>
       </c>
-      <c r="I17" s="14">
-        <v>19</v>
-      </c>
-      <c r="J17" s="14">
-        <v>15</v>
-      </c>
-      <c r="K17" s="15">
-        <v>26.666666666666</v>
-      </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="15">
-        <v>72.727272727272</v>
-      </c>
       <c r="N17" s="15">
-        <v>-32.142857142857</v>
+        <v>-35.483870967741</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
         <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>55.555555555555</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>2.439024390243</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M18" s="15">
-        <v>2.439024390243</v>
+        <v>2.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-64.705882352941</v>
+        <v>-64.341085271317</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.764705882352</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.923076923076</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.931034482758</v>
+        <v>-24.096385542168</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.439024390243</v>
+        <v>-31.521739130434</v>
       </c>
       <c r="M19" s="15">
-        <v>-20.134228187919</v>
+        <v>-26.744186046511</v>
       </c>
       <c r="N19" s="15">
-        <v>-67.307692307692</v>
+        <v>-68.965517241379</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>5</v>
       </c>
       <c r="J20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="15">
         <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.212121212121</v>
+        <v>-96.753246753246</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-4</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.371134020618</v>
+        <v>-24</v>
       </c>
       <c r="I21" s="17">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.439024390243</v>
+        <v>-7.792207792207</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.948616600790</v>
+        <v>-24.468085106383</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.254237288135</v>
+        <v>-20.522388059701</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.358974358974</v>
+        <v>-75.740318906605</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1201,13 +1201,13 @@
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-16.666666666666</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L22" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M22" s="15">
         <v>-41.176470588235</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.166666666666</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.111111111111</v>
+        <v>-8.490566037735</v>
       </c>
       <c r="I24" s="14">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="J24" s="14">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.677966101694</v>
+        <v>-9.448818897637</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.334600760456</v>
+        <v>-21.501706484641</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.957264957265</v>
+        <v>-10.852713178294</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.818181818181</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F25" s="14">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G25" s="14">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.045454545454</v>
+        <v>-22.619047619047</v>
       </c>
       <c r="I25" s="14">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J25" s="14">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.857142857142</v>
+        <v>-23.4375</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.284403669724</v>
+        <v>-40</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>-46.666666666666</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J26" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.843137254901</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.071428571428</v>
+        <v>-20</v>
       </c>
       <c r="M26" s="15">
-        <v>51.612903225806</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-77.777777777777</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-62.5</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="L28" s="15">
-        <v>-53.846153846153</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -936,79 +936,79 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.612903225806</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.384615384615</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="C17" s="14">
         <v>1</v>
       </c>
-      <c r="E17" s="15">
-        <v>-100</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="14">
         <v>16</v>
       </c>
       <c r="K17" s="15">
-        <v>25</v>
+        <v>31.25</v>
       </c>
       <c r="L17" s="15">
-        <v>5.263157894736</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M17" s="15">
-        <v>42.857142857142</v>
+        <v>40</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.483870967741</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>6</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>7.142857142857</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I18" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>53.333333333333</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L18" s="15">
-        <v>4.545454545454</v>
+        <v>4</v>
       </c>
       <c r="M18" s="15">
-        <v>2.222222222222</v>
+        <v>4</v>
       </c>
       <c r="N18" s="15">
-        <v>-64.341085271317</v>
+        <v>-61.764705882352</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-71.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
         <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.714285714285</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.096385542168</v>
+        <v>-22.527472527472</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.521739130434</v>
+        <v>-31.553398058252</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.744186046511</v>
+        <v>-23.783783783783</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.965517241379</v>
+        <v>-67.511520737327</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.753246753246</v>
+        <v>-96.363636363636</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-53.846153846153</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H21" s="18">
-        <v>-24</v>
+        <v>-11.956521739130</v>
       </c>
       <c r="I21" s="17">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="J21" s="17">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.792207792207</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.468085106383</v>
+        <v>-24.761904761904</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.522388059701</v>
+        <v>-17.708333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.740318906605</v>
+        <v>-74.733475479744</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-23.076923076923</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-41.176470588235</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.490566037735</v>
+        <v>-9.909909909909</v>
       </c>
       <c r="I24" s="14">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="J24" s="14">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.448818897637</v>
+        <v>-13.310580204778</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.501706484641</v>
+        <v>-22.796352583586</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.852713178294</v>
+        <v>-14.189189189189</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>11.764705882352</v>
+        <v>-36</v>
       </c>
       <c r="F25" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.619047619047</v>
+        <v>-19.277108433734</v>
       </c>
       <c r="I25" s="14">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J25" s="14">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.4375</v>
+        <v>-24.884792626728</v>
       </c>
       <c r="L25" s="15">
-        <v>-40</v>
+        <v>-40.510948905109</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>19</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.142857142857</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J26" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.698412698412</v>
       </c>
       <c r="L26" s="15">
-        <v>-20</v>
+        <v>-20.289855072463</v>
       </c>
       <c r="M26" s="15">
-        <v>52.941176470588</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-88.888888888888</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
         <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-58.823529411764</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L28" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.827586206896</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.476190476190</v>
+        <v>-92.021276595744</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>5</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H17" s="15">
-        <v>66.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K17" s="15">
-        <v>31.25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>10.526315789473</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>40</v>
+        <v>26.315789473684</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.135135135135</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>38.461538461538</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>52.941176470588</v>
+        <v>51.351351351351</v>
       </c>
       <c r="L18" s="15">
-        <v>4</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M18" s="15">
-        <v>4</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N18" s="15">
-        <v>-61.764705882352</v>
+        <v>-64.556962025316</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.428571428571</v>
+        <v>-39.726027397260</v>
       </c>
       <c r="I19" s="14">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J19" s="14">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.527472527472</v>
+        <v>-24.378109452736</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.553398058252</v>
+        <v>-33.039647577092</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.783783783783</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="N19" s="15">
-        <v>-67.511520737327</v>
+        <v>-68.067226890756</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
         <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M20" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.363636363636</v>
+        <v>-96.089385474860</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.956521739130</v>
+        <v>-27.450980392156</v>
       </c>
       <c r="I21" s="17">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="J21" s="17">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.952380952380</v>
+        <v>-9.574468085106</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.761904761904</v>
+        <v>-26.300578034682</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.708333333333</v>
+        <v>-20.807453416149</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.733475479744</v>
+        <v>-75.480769230769</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-16.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-44.444444444444</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.909909909909</v>
+        <v>-24.347826086956</v>
       </c>
       <c r="I24" s="14">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.310580204778</v>
+        <v>-18.042813455657</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.796352583586</v>
+        <v>-25.555555555555</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.189189189189</v>
+        <v>-14.649681528662</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>-36</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="F25" s="14">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H25" s="15">
-        <v>-19.277108433734</v>
+        <v>-34.408602150537</v>
       </c>
       <c r="I25" s="14">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J25" s="14">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.884792626728</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.510948905109</v>
+        <v>-42.574257425742</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-20.833333333333</v>
+        <v>-34.375</v>
       </c>
       <c r="I26" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J26" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.698412698412</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.289855072463</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="M26" s="15">
-        <v>57.142857142857</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
         <v>50</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,16 +937,16 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
         <v>-50</v>
@@ -955,19 +955,19 @@
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L16" s="15">
-        <v>-55.882352941176</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.333333333333</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.021276595744</v>
+        <v>-92.718446601941</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J17" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K17" s="15">
-        <v>14.285714285714</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L17" s="15">
-        <v>14.285714285714</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M17" s="15">
-        <v>26.315789473684</v>
+        <v>23.809523809523</v>
       </c>
       <c r="N17" s="15">
-        <v>-35.135135135135</v>
+        <v>-43.478260869565</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>51.351351351351</v>
+        <v>53.846153846153</v>
       </c>
       <c r="L18" s="15">
-        <v>7.692307692307</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M18" s="15">
-        <v>3.703703703703</v>
+        <v>5.263157894736</v>
       </c>
       <c r="N18" s="15">
-        <v>-64.556962025316</v>
+        <v>-65.714285714285</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-52.631578947368</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
         <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H19" s="15">
-        <v>-39.726027397260</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="I19" s="14">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.378109452736</v>
+        <v>-23.744292237442</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.039647577092</v>
+        <v>-29.237288135593</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.213592233009</v>
+        <v>-27.074235807860</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.067226890756</v>
+        <v>-68.129770992366</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="L20" s="15">
-        <v>-36.363636363636</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M20" s="15">
         <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.089385474860</v>
+        <v>-96.446700507614</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
         <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.450980392156</v>
+        <v>-28.431372549019</v>
       </c>
       <c r="I21" s="17">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="J21" s="17">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.574468085106</v>
+        <v>-9.771986970684</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.300578034682</v>
+        <v>-24.109589041095</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.807453416149</v>
+        <v>-21.306818181818</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.480769230769</v>
+        <v>-75.933970460469</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-60</v>
+      </c>
+      <c r="I22" s="14">
+        <v>12</v>
+      </c>
+      <c r="J22" s="14">
+        <v>17</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="L22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I22" s="14">
-        <v>11</v>
-      </c>
-      <c r="J22" s="14">
-        <v>15</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-26.666666666666</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-8.333333333333</v>
-      </c>
       <c r="M22" s="15">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-58.823529411764</v>
+        <v>3.703703703703</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.347826086956</v>
+        <v>-17.796610169491</v>
       </c>
       <c r="I24" s="14">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J24" s="14">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.042813455657</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.555555555555</v>
+        <v>-25.316455696202</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.649681528662</v>
+        <v>-13.742690058479</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.068965517241</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" s="14">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.408602150537</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="I25" s="14">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="J25" s="14">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.268292682926</v>
+        <v>-29.588014981273</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.574257425742</v>
+        <v>-43.373493975903</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
         <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.375</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J26" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.808219178082</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.077922077922</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="M26" s="15">
-        <v>53.846153846153</v>
+        <v>40.425531914893</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-71.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-55.555555555555</v>
+        <v>-55</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -911,63 +911,63 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
+        <v>300</v>
+      </c>
+      <c r="M15" s="15">
         <v>100</v>
       </c>
-      <c r="M15" s="15">
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
         <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.052631578947</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.333333333333</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.459459459459</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.718446601941</v>
+        <v>-92.272727272727</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>13.043478260869</v>
+        <v>7.407407407407</v>
       </c>
       <c r="L17" s="15">
-        <v>13.043478260869</v>
+        <v>20.833333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>23.809523809523</v>
+        <v>20.833333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.478260869565</v>
+        <v>-47.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>53.846153846153</v>
+        <v>48.780487804878</v>
       </c>
       <c r="L18" s="15">
-        <v>5.263157894736</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="M18" s="15">
-        <v>5.263157894736</v>
+        <v>5.172413793103</v>
       </c>
       <c r="N18" s="15">
-        <v>-65.714285714285</v>
+        <v>-67.894736842105</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>-40.540540540540</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="J19" s="14">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.744292237442</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.237288135593</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.074235807860</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.129770992366</v>
+        <v>-68.858131487889</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.446700507614</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.431372549019</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="J21" s="17">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.771986970684</v>
+        <v>-9.393939393939</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.109589041095</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.306818181818</v>
+        <v>-20.053475935828</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.933970460469</v>
+        <v>-76.175298804780</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1201,16 +1201,16 @@
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>-29.411764705882</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M22" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>3.703703703703</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.796610169491</v>
+        <v>-32.307692307692</v>
       </c>
       <c r="I24" s="14">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="J24" s="14">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.96875</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.316455696202</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.742690058479</v>
+        <v>-12.983425414364</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.782608695652</v>
+        <v>-43.010752688172</v>
       </c>
       <c r="I25" s="14">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="J25" s="14">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.588014981273</v>
+        <v>-29.824561403508</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.373493975903</v>
+        <v>-43.820224719101</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
         <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>-22.222222222222</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I26" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.512195121951</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M26" s="15">
-        <v>40.425531914893</v>
+        <v>35.849056603773</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-55</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>-47.058823529411</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L31" s="15">
         <v>0</v>
-      </c>
-      <c r="L31" s="15">
-        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
-      </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
         <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.047619047619</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="L16" s="15">
+        <v>-60.465116279069</v>
+      </c>
+      <c r="M16" s="15">
         <v>-56.410256410256</v>
       </c>
-      <c r="M16" s="15">
-        <v>-55.263157894736</v>
-      </c>
       <c r="N16" s="15">
-        <v>-92.272727272727</v>
+        <v>-92.916666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>400</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.272727272727</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>7.407407407407</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>20.833333333333</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>20.833333333333</v>
+        <v>30.769230769230</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.272727272727</v>
+        <v>-42.372881355932</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>48.780487804878</v>
+        <v>43.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.612903225806</v>
+        <v>-1.5625</v>
       </c>
       <c r="M18" s="15">
-        <v>5.172413793103</v>
+        <v>1.612903225806</v>
       </c>
       <c r="N18" s="15">
-        <v>-67.894736842105</v>
+        <v>-69.117647058823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.666666666666</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.470588235294</v>
+        <v>-20.289855072463</v>
       </c>
       <c r="I19" s="14">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J19" s="14">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.115537848605</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.205882352941</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.229508196721</v>
+        <v>-25.283018867924</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.858131487889</v>
+        <v>-68.064516129032</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
@@ -1128,10 +1128,10 @@
         <v>-38.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.153846153846</v>
+        <v>-96.412556053811</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.391304347826</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.191919191919</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="I21" s="17">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="J21" s="17">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.393939393939</v>
+        <v>-8.757062146892</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.529411764705</v>
+        <v>-22.541966426858</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.053475935828</v>
+        <v>-19.851116625310</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.175298804780</v>
+        <v>-76.091783863804</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,25 +1192,25 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L22" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>-42.857142857142</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>55</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.307692307692</v>
+        <v>-17.117117117117</v>
       </c>
       <c r="I24" s="14">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="J24" s="14">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.96875</v>
+        <v>-14.603960396039</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.531914893617</v>
+        <v>-25.646551724137</v>
       </c>
       <c r="M24" s="15">
-        <v>-12.983425414364</v>
+        <v>-10.852713178294</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>17</v>
+      </c>
+      <c r="D25" s="14">
         <v>12</v>
       </c>
-      <c r="D25" s="14">
-        <v>18</v>
-      </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G25" s="14">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.010752688172</v>
+        <v>-32.5</v>
       </c>
       <c r="I25" s="14">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="J25" s="14">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.824561403508</v>
+        <v>-26.936026936026</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.820224719101</v>
+        <v>-44.783715012722</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.545454545454</v>
+        <v>25</v>
       </c>
       <c r="I26" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J26" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.195121951219</v>
+        <v>-4.597701149425</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.631578947368</v>
       </c>
       <c r="M26" s="15">
-        <v>35.849056603773</v>
+        <v>33.870967741935</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-75</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-29.166666666666</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L16" s="15">
-        <v>-60.465116279069</v>
+        <v>-59.574468085106</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.410256410256</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.916666666666</v>
+        <v>-92.607003891050</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>400</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K17" s="15">
-        <v>21.428571428571</v>
+        <v>12.903225806451</v>
       </c>
       <c r="L17" s="15">
-        <v>41.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M17" s="15">
-        <v>30.769230769230</v>
+        <v>20.689655172413</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.372881355932</v>
+        <v>-46.969696969697</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>43.181818181818</v>
+        <v>38.775510204081</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.5625</v>
+        <v>4.615384615384</v>
       </c>
       <c r="M18" s="15">
-        <v>1.612903225806</v>
+        <v>6.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-69.117647058823</v>
+        <v>-68.807339449541</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>5.882352941176</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.289855072463</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="J19" s="14">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.115537848605</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.205882352941</v>
+        <v>-23.448275862069</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.283018867924</v>
+        <v>-21.830985915493</v>
       </c>
       <c r="N19" s="15">
-        <v>-68.064516129032</v>
+        <v>-66.312594840667</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.461538461538</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M20" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.412556053811</v>
+        <v>-96.186440677966</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>36</v>
+      </c>
+      <c r="D21" s="17">
         <v>25</v>
       </c>
-      <c r="D21" s="17">
-        <v>24</v>
-      </c>
       <c r="E21" s="18">
-        <v>4.166666666666</v>
+        <v>44</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.588235294117</v>
+        <v>3.092783505154</v>
       </c>
       <c r="I21" s="17">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="J21" s="17">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.757062146892</v>
+        <v>-5.804749340369</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.541966426858</v>
+        <v>-19.594594594594</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.851116625310</v>
+        <v>-16.976744186046</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.091783863804</v>
+        <v>-75.225537820957</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1198,19 +1198,19 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" s="15">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>-18.75</v>
       </c>
       <c r="M22" s="15">
-        <v>-45.454545454545</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>55</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.117117117117</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="J24" s="14">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.603960396039</v>
+        <v>-11.058823529411</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.646551724137</v>
+        <v>-24.550898203592</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.852713178294</v>
+        <v>-10.426540284360</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>41.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.5</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I25" s="14">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="J25" s="14">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.936026936026</v>
+        <v>-25.079365079365</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.783715012722</v>
+        <v>-43.942992874109</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>120</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>25</v>
+        <v>61.904761904761</v>
       </c>
       <c r="I26" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J26" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.597701149425</v>
+        <v>-1.063829787234</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.631578947368</v>
+        <v>-14.678899082568</v>
       </c>
       <c r="M26" s="15">
-        <v>33.870967741935</v>
+        <v>43.076923076923</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="14">
-        <v>4</v>
-      </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1447,13 +1447,13 @@
         <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-54.545454545454</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="L28" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
         <v>300</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>-29.629629629629</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-59.574468085106</v>
+        <v>-60.784313725490</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.658536585365</v>
+        <v>-53.488372093023</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.607003891050</v>
+        <v>-92.619926199262</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
         <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K17" s="15">
-        <v>12.903225806451</v>
+        <v>15.151515151515</v>
       </c>
       <c r="L17" s="15">
-        <v>25</v>
+        <v>18.75</v>
       </c>
       <c r="M17" s="15">
-        <v>20.689655172413</v>
+        <v>31.034482758620</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.969696969697</v>
+        <v>-46.478873239436</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>38.775510204081</v>
+        <v>40.384615384615</v>
       </c>
       <c r="L18" s="15">
-        <v>4.615384615384</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="M18" s="15">
-        <v>6.25</v>
+        <v>7.352941176470</v>
       </c>
       <c r="N18" s="15">
-        <v>-68.807339449541</v>
+        <v>-69.456066945606</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>11.290322580645</v>
       </c>
       <c r="I19" s="14">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="J19" s="14">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.909090909090</v>
+        <v>-15.658362989323</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.448275862069</v>
+        <v>-22.039473684210</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.830985915493</v>
+        <v>-21.262458471760</v>
       </c>
       <c r="N19" s="15">
-        <v>-66.312594840667</v>
+        <v>-65.899280575539</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
+        <v>200</v>
+      </c>
+      <c r="I20" s="14">
+        <v>10</v>
+      </c>
+      <c r="J20" s="14">
+        <v>5</v>
+      </c>
+      <c r="K20" s="15">
         <v>100</v>
       </c>
-      <c r="I20" s="14">
-        <v>9</v>
-      </c>
-      <c r="J20" s="14">
-        <v>4</v>
-      </c>
-      <c r="K20" s="15">
-        <v>125</v>
-      </c>
       <c r="L20" s="15">
-        <v>-30.769230769230</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.186440677966</v>
+        <v>-95.951417004048</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>44</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>3.092783505154</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I21" s="17">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="J21" s="17">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.804749340369</v>
+        <v>-5.911330049261</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.594594594594</v>
+        <v>-20.250521920668</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.976744186046</v>
+        <v>-15.859030837004</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.225537820957</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="14">
         <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" s="15">
-        <v>-38.095238095238</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L22" s="15">
         <v>-18.75</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>57.142857142857</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G24" s="14">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>14.285714285714</v>
+        <v>8.910891089108</v>
       </c>
       <c r="I24" s="14">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="J24" s="14">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.058823529411</v>
+        <v>-11.208791208791</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.550898203592</v>
+        <v>-25.185185185185</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.426540284360</v>
+        <v>-11.403508771929</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>11.111111111111</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G25" s="14">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.695652173913</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I25" s="14">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="J25" s="14">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.079365079365</v>
+        <v>-23.100303951367</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.942992874109</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>42.857142857142</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>61.904761904761</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.063829787234</v>
+        <v>-9.345794392523</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.678899082568</v>
+        <v>-17.094017094017</v>
       </c>
       <c r="M26" s="15">
-        <v>43.076923076923</v>
+        <v>29.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
         <v>200</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-56.521739130434</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L31" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>300</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-20</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.125</v>
       </c>
       <c r="L16" s="15">
-        <v>-60.784313725490</v>
+        <v>-56.603773584905</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.488372093023</v>
+        <v>-48.888888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.619926199262</v>
+        <v>-91.901408450704</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
         <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I17" s="14">
+        <v>43</v>
+      </c>
+      <c r="J17" s="14">
         <v>38</v>
       </c>
-      <c r="J17" s="14">
-        <v>33</v>
-      </c>
       <c r="K17" s="15">
-        <v>15.151515151515</v>
+        <v>13.157894736842</v>
       </c>
       <c r="L17" s="15">
-        <v>18.75</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M17" s="15">
-        <v>31.034482758620</v>
+        <v>48.275862068965</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.478873239436</v>
+        <v>-43.421052631578</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="I18" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>40.384615384615</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.947368421052</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M18" s="15">
-        <v>7.352941176470</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-69.456066945606</v>
+        <v>-70.428015564202</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.764705882352</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>11.290322580645</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I19" s="14">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.658362989323</v>
+        <v>-15.050167224080</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.039473684210</v>
+        <v>-23.262839879154</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.262458471760</v>
+        <v>-20.125786163522</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.899280575539</v>
+        <v>-65.951742627345</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
@@ -1116,22 +1116,22 @@
         <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.951417004048</v>
+        <v>-95.801526717557</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>3.030303030303</v>
+        <v>4.716981132075</v>
       </c>
       <c r="I21" s="17">
-        <v>382</v>
+        <v>411</v>
       </c>
       <c r="J21" s="17">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.911330049261</v>
+        <v>-5.733944954128</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.250521920668</v>
+        <v>-20.502901353965</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.859030837004</v>
+        <v>-13.655462184873</v>
       </c>
       <c r="N21" s="18">
-        <v>-75</v>
+        <v>-74.785276073619</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K22" s="15">
-        <v>-40.909090909090</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="L22" s="15">
-        <v>-18.75</v>
+        <v>-6.25</v>
       </c>
       <c r="M22" s="15">
-        <v>-40.909090909090</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.333333333333</v>
+        <v>8</v>
       </c>
       <c r="F24" s="14">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>8.910891089108</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="J24" s="14">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.208791208791</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.185185185185</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.403508771929</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>14.285714285714</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G25" s="14">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H25" s="15">
-        <v>6.451612903225</v>
+        <v>35.849056603773</v>
       </c>
       <c r="I25" s="14">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="J25" s="14">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K25" s="15">
-        <v>-23.100303951367</v>
+        <v>-19.822485207100</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.902439024390</v>
+        <v>-43.067226890756</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-69.230769230769</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
+        <v>37</v>
+      </c>
+      <c r="G26" s="14">
         <v>31</v>
       </c>
-      <c r="G26" s="14">
-        <v>29</v>
-      </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.345794392523</v>
+        <v>-4.424778761061</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.094017094017</v>
+        <v>-10</v>
       </c>
       <c r="M26" s="15">
-        <v>29.333333333333</v>
+        <v>35</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-57.692307692307</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-45</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1570,13 +1570,13 @@
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-006pct.xlsx
+++ b/data/source/weekly/cs-en-us-006pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,45 +902,45 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M15" s="15">
+        <v>25</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
@@ -955,19 +955,19 @@
         <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.125</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-56.603773584905</v>
+        <v>-58.928571428571</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.888888888888</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.901408450704</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
-      <c r="E17" s="15">
-        <v>-40</v>
+        <v>6</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>9.090909090909</v>
+        <v>30</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
         <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>13.157894736842</v>
+        <v>28.947368421052</v>
       </c>
       <c r="L17" s="15">
-        <v>26.470588235294</v>
+        <v>22.5</v>
       </c>
       <c r="M17" s="15">
-        <v>48.275862068965</v>
+        <v>53.125</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.421052631578</v>
+        <v>-40.243902439024</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
         <v>15</v>
       </c>
-      <c r="G18" s="14">
-        <v>16</v>
-      </c>
       <c r="H18" s="15">
-        <v>-6.25</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>76</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>33.333333333333</v>
+        <v>28.813559322033</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.317073170731</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="M18" s="15">
-        <v>11.764705882352</v>
+        <v>4.109589041095</v>
       </c>
       <c r="N18" s="15">
-        <v>-70.428015564202</v>
+        <v>-71.851851851851</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.555555555555</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>15.384615384615</v>
+        <v>8.571428571428</v>
       </c>
       <c r="I19" s="14">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="J19" s="14">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.050167224080</v>
+        <v>-14.953271028037</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.262839879154</v>
+        <v>-22</v>
       </c>
       <c r="M19" s="15">
-        <v>-20.125786163522</v>
+        <v>-19.469026548672</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.951742627345</v>
+        <v>-65.832290362953</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.25</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.801526717557</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.333333333333</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>4.716981132075</v>
+        <v>3.669724770642</v>
       </c>
       <c r="I21" s="17">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="J21" s="17">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.733944954128</v>
+        <v>-5.399568034557</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.502901353965</v>
+        <v>-21.223021582733</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.655462184873</v>
+        <v>-13.438735177865</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.785276073619</v>
+        <v>-74.608695652173</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>5</v>
-      </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
         <v>23</v>
       </c>
       <c r="K22" s="15">
-        <v>-34.782608695652</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L22" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-34.782608695652</v>
+        <v>-36</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>8</v>
+        <v>19.230769230769</v>
       </c>
       <c r="F24" s="14">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15">
-        <v>20.833333333333</v>
+        <v>15.686274509803</v>
       </c>
       <c r="I24" s="14">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="J24" s="14">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.416666666666</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.862068965517</v>
+        <v>-24.013157894736</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.340206185567</v>
+        <v>-11.324376199616</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" s="14">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>35.849056603773</v>
+        <v>12.307692307692</v>
       </c>
       <c r="I25" s="14">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="J25" s="14">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="K25" s="15">
-        <v>-19.822485207100</v>
+        <v>-20.165745856353</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.067226890756</v>
+        <v>-41.851106639839</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>19.354838709677</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.424778761061</v>
+        <v>-7.377049180327</v>
       </c>
       <c r="L26" s="15">
-        <v>-10</v>
+        <v>-11.023622047244</v>
       </c>
       <c r="M26" s="15">
-        <v>35</v>
+        <v>34.523809523809</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="I28" s="14">
+        <v>14</v>
+      </c>
+      <c r="J28" s="14">
+        <v>29</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-51.724137931034</v>
+      </c>
+      <c r="L28" s="15">
         <v>-33.333333333333</v>
-      </c>
-      <c r="I28" s="14">
-        <v>12</v>
-      </c>
-      <c r="J28" s="14">
-        <v>28</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
